--- a/hall/resources/sample/SeasonShop.xlsx
+++ b/hall/resources/sample/SeasonShop.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -224,6 +224,15 @@
   </si>
   <si>
     <t>1960000_900</t>
+  </si>
+  <si>
+    <t>1130001_1</t>
+  </si>
+  <si>
+    <t>挑战券</t>
+  </si>
+  <si>
+    <t>1980000_100</t>
   </si>
 </sst>
 </file>
@@ -877,9 +886,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -901,6 +913,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1427,7 +1442,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
@@ -1442,604 +1457,634 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <f t="shared" ref="A5:A20" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>1131001</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="G5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
         <v>5</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="7"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>1002</v>
       </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>1131002</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="G6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
         <v>5</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="7"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>1003</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>1131003</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <v>5</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="7"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>1004</v>
       </c>
-      <c r="B8" s="6">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="B8" s="7">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>1131004</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="G8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
         <v>5</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="7"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="7">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>1131005</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="G9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
         <v>5</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="7"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>1006</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>1131006</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="G10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
         <v>5</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="7"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>1007</v>
       </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>1130002</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="6" t="b">
+      <c r="G11" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="7"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>1008</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B12" s="7">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7">
         <v>8</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>1130003</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="6" t="b">
+      <c r="G12" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="7"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>2001</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>2</v>
       </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>1131001</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="G13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
         <v>5</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>2002</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>2</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>2</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>1131002</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="G14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
         <v>5</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>2003</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>2</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>3</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>1131003</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="G15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
         <v>5</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>2</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>4</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>1131004</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
         <v>5</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>2</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>5</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>1131005</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
         <v>5</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="2"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>2006</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>2</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>6</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>1131006</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="G18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
         <v>5</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>2007</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>2</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>7</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>1130002</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="1" t="b">
+      <c r="G19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="1">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J19" s="2"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="1">
+      <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>2008</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>2</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>8</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>1130003</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="1" t="b">
+      <c r="G20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:10">
+      <c r="A21" s="2">
+        <f>B21*1000+C21</f>
+        <v>2009</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1130001</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>20</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/SeasonShop.xlsx
+++ b/hall/resources/sample/SeasonShop.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -83,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -112,6 +117,9 @@
     <t>购买价格</t>
   </si>
   <si>
+    <t>是否开启</t>
+  </si>
+  <si>
     <t>客户端资源</t>
   </si>
   <si>
@@ -151,6 +159,9 @@
     <t>cost</t>
   </si>
   <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
     <t>icon</t>
   </si>
   <si>
@@ -226,6 +237,12 @@
     <t>1960000_900</t>
   </si>
   <si>
+    <t>1960000_1000</t>
+  </si>
+  <si>
+    <t>1960000_1500</t>
+  </si>
+  <si>
     <t>1130001_1</t>
   </si>
   <si>
@@ -233,6 +250,57 @@
   </si>
   <si>
     <t>1980000_100</t>
+  </si>
+  <si>
+    <t>1024001_1</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>1960000_100</t>
+  </si>
+  <si>
+    <t>1024005_1</t>
+  </si>
+  <si>
+    <t>研究点</t>
+  </si>
+  <si>
+    <t>1024007_1</t>
+  </si>
+  <si>
+    <t>加速卡</t>
+  </si>
+  <si>
+    <t>1024008_10</t>
+  </si>
+  <si>
+    <t>胜运砾石</t>
+  </si>
+  <si>
+    <t>1024009_10</t>
+  </si>
+  <si>
+    <t>鸿运原石</t>
+  </si>
+  <si>
+    <t>1024010_10</t>
+  </si>
+  <si>
+    <t>幸运宝石</t>
+  </si>
+  <si>
+    <t>1024013_1</t>
+  </si>
+  <si>
+    <t>游客邀请函</t>
+  </si>
+  <si>
+    <t>1024014_1</t>
+  </si>
+  <si>
+    <t>雇员邀请函</t>
   </si>
 </sst>
 </file>
@@ -1442,21 +1510,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="11.125" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
     <col min="7" max="7" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="10" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="12" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1487,68 +1556,77 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1559,10 +1637,11 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="7">
-        <f t="shared" ref="A5:A20" si="0">B5*1000+C5</f>
+        <f t="shared" ref="A5:A21" si="0">B5*1000+C5</f>
         <v>1001</v>
       </c>
       <c r="B5" s="7">
@@ -1572,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="7">
         <v>1131001</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="7" t="b">
         <v>1</v>
@@ -1587,11 +1666,14 @@
         <v>5</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>1002</v>
@@ -1603,13 +1685,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="7">
         <v>1131002</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>1</v>
@@ -1618,11 +1700,14 @@
         <v>5</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10">
+        <v>30</v>
+      </c>
+      <c r="J6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>1003</v>
@@ -1634,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7" s="7">
         <v>1131003</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" s="7" t="b">
         <v>1</v>
@@ -1649,11 +1734,14 @@
         <v>5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -1665,13 +1753,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="7">
         <v>1131004</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G8" s="7" t="b">
         <v>1</v>
@@ -1680,11 +1768,14 @@
         <v>5</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10">
+        <v>36</v>
+      </c>
+      <c r="J8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -1696,13 +1787,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="7">
         <v>1131005</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G9" s="7" t="b">
         <v>1</v>
@@ -1711,11 +1802,14 @@
         <v>5</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10">
+        <v>39</v>
+      </c>
+      <c r="J9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -1727,13 +1821,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" s="7">
         <v>1131006</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>1</v>
@@ -1742,11 +1836,14 @@
         <v>5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10">
+        <v>42</v>
+      </c>
+      <c r="J10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -1758,13 +1855,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="7">
         <v>1130002</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11" s="7" t="b">
         <v>0</v>
@@ -1773,11 +1870,14 @@
         <v>1</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10">
+        <v>45</v>
+      </c>
+      <c r="J11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -1789,13 +1889,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E12" s="7">
         <v>1130003</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G12" s="7" t="b">
         <v>0</v>
@@ -1804,11 +1904,14 @@
         <v>1</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10">
+        <v>48</v>
+      </c>
+      <c r="J12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>2001</v>
@@ -1820,13 +1923,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2">
         <v>1131001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2" t="b">
         <v>1</v>
@@ -1835,11 +1938,14 @@
         <v>5</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>2002</v>
@@ -1851,13 +1957,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="2">
         <v>1131002</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="2" t="b">
         <v>1</v>
@@ -1866,11 +1972,14 @@
         <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>2003</v>
@@ -1882,13 +1991,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2">
         <v>1131003</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="b">
         <v>1</v>
@@ -1897,11 +2006,14 @@
         <v>5</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>2004</v>
@@ -1913,13 +2025,13 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2">
         <v>1131004</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="b">
         <v>1</v>
@@ -1928,11 +2040,14 @@
         <v>5</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>2005</v>
@@ -1944,13 +2059,13 @@
         <v>5</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2">
         <v>1131005</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" s="2" t="b">
         <v>1</v>
@@ -1959,11 +2074,14 @@
         <v>5</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10">
+        <v>33</v>
+      </c>
+      <c r="J17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>2006</v>
@@ -1975,13 +2093,13 @@
         <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2">
         <v>1131006</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G18" s="2" t="b">
         <v>1</v>
@@ -1990,11 +2108,14 @@
         <v>5</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="1:10">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>2007</v>
@@ -2006,13 +2127,13 @@
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2">
         <v>1130002</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="2" t="b">
         <v>0</v>
@@ -2021,11 +2142,14 @@
         <v>1</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10">
+        <v>49</v>
+      </c>
+      <c r="J19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>2008</v>
@@ -2037,13 +2161,13 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2">
         <v>1130003</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G20" s="2" t="b">
         <v>0</v>
@@ -2052,13 +2176,16 @@
         <v>1</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:10">
+        <v>50</v>
+      </c>
+      <c r="J20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:11">
       <c r="A21" s="2">
-        <f>B21*1000+C21</f>
+        <f t="shared" si="0"/>
         <v>2009</v>
       </c>
       <c r="B21" s="2">
@@ -2068,13 +2195,13 @@
         <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E21" s="1">
         <v>1130001</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G21" s="2" t="b">
         <v>1</v>
@@ -2083,8 +2210,281 @@
         <v>20</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>49</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="J21" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="2">
+        <f t="shared" ref="A22:A29" si="1">B22*1000+C22</f>
+        <v>2010</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1024001</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="2">
+        <f t="shared" si="1"/>
+        <v>2011</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1024005</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="2">
+        <f t="shared" si="1"/>
+        <v>2012</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2">
+        <v>12</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1024007</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="2">
+        <f t="shared" si="1"/>
+        <v>2013</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2">
+        <v>13</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1024008</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2">
+        <f t="shared" si="1"/>
+        <v>2014</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>14</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1024009</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="2">
+        <f t="shared" si="1"/>
+        <v>2015</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1024010</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="2">
+        <f t="shared" si="1"/>
+        <v>2016</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <v>16</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1024013</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>10</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="2">
+        <f t="shared" si="1"/>
+        <v>2017</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>17</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1024014</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="D31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/SeasonShop.xlsx
+++ b/hall/resources/sample/SeasonShop.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>雇员邀请函</t>
+  </si>
+  <si>
+    <t>1131007_1</t>
+  </si>
+  <si>
+    <t>挂机收益.白</t>
   </si>
 </sst>
 </file>
@@ -954,7 +960,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -984,6 +990,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2481,7 +2490,37 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="D30" s="1"/>
+      <c r="A30" s="2">
+        <f>B30*1000+C30</f>
+        <v>2018</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2">
+        <v>18</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1131007</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10">
+        <v>5</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:11">
       <c r="D31" s="1"/>
